--- a/reports/combined_data.xlsx
+++ b/reports/combined_data.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mark-Houwink" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flory" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failures" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aggregated Flory" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aggregated Mark-Houwink" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -469,6 +471,7 @@
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,6 +530,11 @@
           <t>a Transformation</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Failed Field</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -578,6 +586,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -629,6 +642,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -680,6 +698,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -731,6 +754,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -782,6 +810,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -833,6 +866,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -884,6 +922,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -935,6 +978,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -986,6 +1034,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1037,6 +1090,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1088,6 +1146,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1139,6 +1202,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1190,6 +1258,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1241,6 +1314,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1292,6 +1370,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1341,6 +1424,11 @@
       <c r="K17" s="2" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1369,6 +1457,7 @@
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1427,6 +1516,11 @@
           <t>v Transformation</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Failed Field</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1476,6 +1570,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1525,6 +1624,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1574,6 +1678,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1623,6 +1732,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1672,6 +1786,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1721,6 +1840,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1770,6 +1894,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1819,6 +1948,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1868,6 +2002,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1917,6 +2056,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1966,6 +2110,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2015,6 +2164,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2064,6 +2218,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2113,6 +2272,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2162,6 +2326,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2211,6 +2380,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2260,6 +2434,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2309,6 +2488,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2358,6 +2542,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>polymer_name</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2407,6 +2596,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2456,6 +2650,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2505,6 +2704,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2554,6 +2758,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2603,6 +2812,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2652,6 +2866,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2701,6 +2920,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2750,6 +2974,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2799,6 +3028,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2848,6 +3082,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2897,6 +3136,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2946,6 +3190,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2995,6 +3244,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3044,6 +3298,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3093,6 +3352,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3142,6 +3406,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3191,6 +3460,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3240,6 +3514,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3289,6 +3568,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3338,6 +3622,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>solvent</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3387,6 +3676,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3436,6 +3730,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3485,6 +3784,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3534,6 +3838,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>solvent</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3583,6 +3892,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3632,6 +3946,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3681,6 +4000,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>solvent</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3728,6 +4052,11 @@
       <c r="K48" s="2" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3890,4 +4219,1100 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="82" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Solvent</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Polymer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>c Values</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>v Values</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>acetone</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>[-7.56]</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>[0.5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acetone</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene glycol) methyl ether acrylate</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>[-8.01]</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>[0.39]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>acetone</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>[-7.74]</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>[0.44]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>acetone-d6</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>[-7.673502333065918, -7.94]</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>[0.474477, 0.41]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>acetone-d6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate-block-poly(ethylene glycol) methyl ether methacrylate)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>[-7.797]</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>[0.4355]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>acetone-d6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>[-7.679147780168245, -7.78]</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>[0.452089, 0.43]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>acetonitrile-d3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>[-7.590203777049215, -7.88]</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>[0.515853, 0.44]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>benzene</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>[-7.83]</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>[0.51]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>benzene</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>[-7.91]</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>[0.48]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>benzene</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>[-7.7]</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>[0.54]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>benzene-d6</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>[-7.683956229316216]</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>[0.530394]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>benzene-d6</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>[-7.718505297869414, -7.94]</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>[0.5283, 0.49]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>chloroform</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>[-7.86]</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>[0.5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>chloroform-d</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>[-8.04]</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>[0.45]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>chloroform-d</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>[-7.579851091223765]</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>[0.543219]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>chloroform-d</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>[-7.630222150689829, -7.97]</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>[0.534677, 0.46]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>deuterium oxide</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>dextran</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>[-8.14]</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>[0.47]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>deuterium oxide</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>[-8.101177771017927, -8.39, -8.23]</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>[0.512155, 0.47, 0.49]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>deuterium oxide</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>pullulane</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>[-8.2]</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>[0.49]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>dichloromethane</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>[-7.48967889681907]</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>[0.53678]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>dichloromethane</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>[-7.56166654250548]</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>[0.521453]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>dimethyl sulfoxide</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>[-8.505773029599105]</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>[0.444236]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>methanol-d4</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>[-7.843617451027789, -8.06]</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>[0.504105, 0.45]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>[-8.02]</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>[0.43]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>[-7.733838887780599, -7.94, -8.04]</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>[0.513725, 0.46, 0.45]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>[-7.61465473895388]</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>[0.517608]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>[-7.655839673984551, -8.07]</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>[0.519361, 0.42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>toluene</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>[-7.72, -8.11]</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>[0.5, 0.43]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>toluene-d8</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>[-7.6700776226075575, -7.82]</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>[0.531065, 0.51]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene glycol) methyl ether acrylate</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>[-8.31]</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>[0.47]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Solvent</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Polymer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>K Values</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>a Values</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>acetone-d6</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>[0.06862]</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>[0.56535]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acetone-d6</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>[0.07135]</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>[0.49819]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>acetonitrile-d3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>[0.02456]</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>[0.68948]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>benzene-d6</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>[0.00848]</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>[0.7331]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>benzene-d6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>[0.01077]</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>[0.72682]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>chloroform-d</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>[0.00517]</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>[0.77158]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>chloroform-d</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>[0.00732]</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>[0.74596]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>deuterium oxide</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>[0.02554]</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>[0.67839]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>dichloromethane</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>[0.00702]</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>[0.75226]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>dichloromethane</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>[0.01155]</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>[0.70628]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>dimethyl sulfoxide</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>[0.05265]</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>[0.47463]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>methanol-d4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>[0.03563]</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>[0.65424]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>[0.02417]</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>[0.6831]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>[0.01061]</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>[0.69474]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>[0.0141]</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>[0.7]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>toluene-d8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>[0.0098]</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>[0.73512]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/reports/combined_data.xlsx
+++ b/reports/combined_data.xlsx
@@ -10,8 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mark-Houwink" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flory" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failures" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aggregated Flory" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aggregated Mark-Houwink" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -166,6 +164,2451 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Mark-Houwink Calibration Curves (log-log Plot)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$2:$T$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$3:$T$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$4:$T$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$5:$T$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$6:$T$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$7:$T$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E26B0A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$8:$T$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$9:$T$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$10:$T$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$11:$T$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="10"/>
+          <order val="10"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$12:$T$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$13:$T$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$14:$T$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="13"/>
+          <order val="13"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$15:$T$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="14"/>
+          <order val="14"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$16:$T$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="15"/>
+          <order val="15"/>
+          <tx>
+            <strRef>
+              <f>'Mark-Houwink'!R17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E26B0A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Mark-Houwink'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mark-Houwink'!$S$17:$T$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log(M / g mol⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="3.03"/>
+          <min val="-0.47"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log([eta] / mL g⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="13"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Flory Calibration Curves (log-log Plot)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$2:$T$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$3:$T$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$4:$T$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$5:$T$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$6:$T$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$7:$T$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E26B0A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$8:$T$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$9:$T$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$10:$T$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$11:$T$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="10"/>
+          <order val="10"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$12:$T$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$13:$T$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$14:$T$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="13"/>
+          <order val="13"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$15:$T$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="14"/>
+          <order val="14"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$16:$T$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="15"/>
+          <order val="15"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E26B0A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$17:$T$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="16"/>
+          <order val="16"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$18:$T$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="17"/>
+          <order val="17"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$19:$T$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="18"/>
+          <order val="18"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$20:$T$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="19"/>
+          <order val="19"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$21:$T$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="20"/>
+          <order val="20"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$22:$T$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="21"/>
+          <order val="21"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R23</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$23:$T$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="22"/>
+          <order val="22"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R24</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$24:$T$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="23"/>
+          <order val="23"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$25:$T$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="24"/>
+          <order val="24"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E26B0A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$26:$T$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="25"/>
+          <order val="25"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$27:$T$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="26"/>
+          <order val="26"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$28:$T$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="27"/>
+          <order val="27"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$29:$T$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="28"/>
+          <order val="28"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R30</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$30:$T$30</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="29"/>
+          <order val="29"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R31</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$31:$T$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="30"/>
+          <order val="30"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R32</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$32:$T$32</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="31"/>
+          <order val="31"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R33</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$33:$T$33</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="32"/>
+          <order val="32"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R34</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$34:$T$34</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="33"/>
+          <order val="33"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R35</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E26B0A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$35:$T$35</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="34"/>
+          <order val="34"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$36:$T$36</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="35"/>
+          <order val="35"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R37</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$37:$T$37</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="36"/>
+          <order val="36"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R38</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$38:$T$38</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="37"/>
+          <order val="37"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R39</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$39:$T$39</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="38"/>
+          <order val="38"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R40</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$40:$T$40</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="39"/>
+          <order val="39"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R41</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$41:$T$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="40"/>
+          <order val="40"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R42</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$42:$T$42</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="41"/>
+          <order val="41"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R43</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$43:$T$43</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="42"/>
+          <order val="42"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R44</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E26B0A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$44:$T$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="43"/>
+          <order val="43"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R45</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$45:$T$45</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="44"/>
+          <order val="44"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R46</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$46:$T$46</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="45"/>
+          <order val="45"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R47</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$47:$T$47</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="46"/>
+          <order val="46"/>
+          <tx>
+            <strRef>
+              <f>'Flory'!R48</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Flory'!$S$1:$T$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Flory'!$S$48:$T$48</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log(M / g mol⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="-8.539999999999999"/>
+          <min val="-11.71"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>log(D / m² s⁻¹)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -457,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -472,6 +2915,14 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="58" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,6 +2986,32 @@
           <t>Failed Field</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Solvent</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Polymer</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -591,6 +3068,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>acetone-d6</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in tetrahydrofuran-d8 (test1)</t>
+        </is>
+      </c>
+      <c r="S2" s="3">
+        <f>LOG10(H2)+J2*3</f>
+        <v/>
+      </c>
+      <c r="T2" s="3">
+        <f>LOG10(H2)+J2*6</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -647,6 +3150,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>acetone-d6</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in chloroform-d (test1)</t>
+        </is>
+      </c>
+      <c r="S3" s="3">
+        <f>LOG10(H3)+J3*3</f>
+        <v/>
+      </c>
+      <c r="T3" s="3">
+        <f>LOG10(H3)+J3*6</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -703,6 +3232,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>acetonitrile-d3</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in benzene-d6 (test1)</t>
+        </is>
+      </c>
+      <c r="S4" s="3">
+        <f>LOG10(H4)+J4*3</f>
+        <v/>
+      </c>
+      <c r="T4" s="3">
+        <f>LOG10(H4)+J4*6</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -759,6 +3314,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>benzene-d6</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in toluene-d8 (test1)</t>
+        </is>
+      </c>
+      <c r="S5" s="3">
+        <f>LOG10(H5)+J5*3</f>
+        <v/>
+      </c>
+      <c r="T5" s="3">
+        <f>LOG10(H5)+J5*6</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -815,6 +3396,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>benzene-d6</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in dichloromethane (test1)</t>
+        </is>
+      </c>
+      <c r="S6" s="3">
+        <f>LOG10(H6)+J6*3</f>
+        <v/>
+      </c>
+      <c r="T6" s="3">
+        <f>LOG10(H6)+J6*6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -871,6 +3478,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>chloroform-d</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in acetone-d6 (test1)</t>
+        </is>
+      </c>
+      <c r="S7" s="3">
+        <f>LOG10(H7)+J7*3</f>
+        <v/>
+      </c>
+      <c r="T7" s="3">
+        <f>LOG10(H7)+J7*6</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -927,6 +3560,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>chloroform-d</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in methanol-d4 (test1)</t>
+        </is>
+      </c>
+      <c r="S8" s="3">
+        <f>LOG10(H8)+J8*3</f>
+        <v/>
+      </c>
+      <c r="T8" s="3">
+        <f>LOG10(H8)+J8*6</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -983,6 +3642,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>deuterium oxide</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in deuterium oxide (test1)</t>
+        </is>
+      </c>
+      <c r="S9" s="3">
+        <f>LOG10(H9)+J9*3</f>
+        <v/>
+      </c>
+      <c r="T9" s="3">
+        <f>LOG10(H9)+J9*6</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1039,6 +3724,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>dichloromethane</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in tetrahydrofuran-d8 (test1)</t>
+        </is>
+      </c>
+      <c r="S10" s="3">
+        <f>LOG10(H10)+J10*3</f>
+        <v/>
+      </c>
+      <c r="T10" s="3">
+        <f>LOG10(H10)+J10*6</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1095,6 +3806,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>dichloromethane</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in acetonitrile-d3 (test1)</t>
+        </is>
+      </c>
+      <c r="S11" s="3">
+        <f>LOG10(H11)+J11*3</f>
+        <v/>
+      </c>
+      <c r="T11" s="3">
+        <f>LOG10(H11)+J11*6</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1151,6 +3888,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>dimethyl sulfoxide</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in acetone-d6 (test1)</t>
+        </is>
+      </c>
+      <c r="S12" s="3">
+        <f>LOG10(H12)+J12*3</f>
+        <v/>
+      </c>
+      <c r="T12" s="3">
+        <f>LOG10(H12)+J12*6</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1207,6 +3970,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>methanol-d4</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in tetrahydrofuran-d8 (test1)</t>
+        </is>
+      </c>
+      <c r="S13" s="3">
+        <f>LOG10(H13)+J13*3</f>
+        <v/>
+      </c>
+      <c r="T13" s="3">
+        <f>LOG10(H13)+J13*6</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1263,6 +4052,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in chloroform-d (test1)</t>
+        </is>
+      </c>
+      <c r="S14" s="3">
+        <f>LOG10(H14)+J14*3</f>
+        <v/>
+      </c>
+      <c r="T14" s="3">
+        <f>LOG10(H14)+J14*6</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1319,6 +4134,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in benzene-d6 (test1)</t>
+        </is>
+      </c>
+      <c r="S15" s="3">
+        <f>LOG10(H15)+J15*3</f>
+        <v/>
+      </c>
+      <c r="T15" s="3">
+        <f>LOG10(H15)+J15*6</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1375,6 +4216,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in dichloromethane (test1)</t>
+        </is>
+      </c>
+      <c r="S16" s="3">
+        <f>LOG10(H16)+J16*3</f>
+        <v/>
+      </c>
+      <c r="T16" s="3">
+        <f>LOG10(H16)+J16*6</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1431,9 +4298,36 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>toluene-d8</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in dimethyl sulfoxide (test1)</t>
+        </is>
+      </c>
+      <c r="S17" s="3">
+        <f>LOG10(H17)+J17*3</f>
+        <v/>
+      </c>
+      <c r="T17" s="3">
+        <f>LOG10(H17)+J17*6</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1443,7 +4337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1458,6 +4352,14 @@
     <col width="29" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="82" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="104" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1521,6 +4423,32 @@
           <t>Failed Field</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Solvent</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Polymer</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1575,6 +4503,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>acetone</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate)</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in tetrahydrofuran-d8 (test1)</t>
+        </is>
+      </c>
+      <c r="S2" s="3">
+        <f>H2-J2*3</f>
+        <v/>
+      </c>
+      <c r="T2" s="3">
+        <f>H2-J2*6</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1629,6 +4583,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>acetone</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene glycol) methyl ether acrylate</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in chloroform-d (test1)</t>
+        </is>
+      </c>
+      <c r="S3" s="3">
+        <f>H3-J3*3</f>
+        <v/>
+      </c>
+      <c r="T3" s="3">
+        <f>H3-J3*6</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +4663,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>acetone</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in benzene-d6 (test1)</t>
+        </is>
+      </c>
+      <c r="S4" s="3">
+        <f>H4-J4*3</f>
+        <v/>
+      </c>
+      <c r="T4" s="3">
+        <f>H4-J4*6</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1737,6 +4743,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>acetone-d6</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in toluene-d8 (test1)</t>
+        </is>
+      </c>
+      <c r="S5" s="3">
+        <f>H5-J5*3</f>
+        <v/>
+      </c>
+      <c r="T5" s="3">
+        <f>H5-J5*6</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1791,6 +4823,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>acetone-d6</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate-block-poly(ethylene glycol) methyl ether methacrylate)</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in dichloromethane (test1)</t>
+        </is>
+      </c>
+      <c r="S6" s="3">
+        <f>H6-J6*3</f>
+        <v/>
+      </c>
+      <c r="T6" s="3">
+        <f>H6-J6*6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1845,6 +4903,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>acetone-d6</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in acetone-d6 (test1)</t>
+        </is>
+      </c>
+      <c r="S7" s="3">
+        <f>H7-J7*3</f>
+        <v/>
+      </c>
+      <c r="T7" s="3">
+        <f>H7-J7*6</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1899,6 +4983,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>acetonitrile-d3</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in methanol-d4 (test1)</t>
+        </is>
+      </c>
+      <c r="S8" s="3">
+        <f>H8-J8*3</f>
+        <v/>
+      </c>
+      <c r="T8" s="3">
+        <f>H8-J8*6</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1953,6 +5063,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>benzene</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate)</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in deuterium oxide (test1)</t>
+        </is>
+      </c>
+      <c r="S9" s="3">
+        <f>H9-J9*3</f>
+        <v/>
+      </c>
+      <c r="T9" s="3">
+        <f>H9-J9*6</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2007,6 +5143,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>benzene</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in tetrahydrofuran-d8 (test1)</t>
+        </is>
+      </c>
+      <c r="S10" s="3">
+        <f>H10-J10*3</f>
+        <v/>
+      </c>
+      <c r="T10" s="3">
+        <f>H10-J10*6</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2061,6 +5223,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>benzene</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in acetonitrile-d3 (test1)</t>
+        </is>
+      </c>
+      <c r="S11" s="3">
+        <f>H11-J11*3</f>
+        <v/>
+      </c>
+      <c r="T11" s="3">
+        <f>H11-J11*6</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2115,6 +5303,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>benzene-d6</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in acetone-d6 (test1)</t>
+        </is>
+      </c>
+      <c r="S12" s="3">
+        <f>H12-J12*3</f>
+        <v/>
+      </c>
+      <c r="T12" s="3">
+        <f>H12-J12*6</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2169,6 +5383,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>benzene-d6</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in tetrahydrofuran-d8 (test1)</t>
+        </is>
+      </c>
+      <c r="S13" s="3">
+        <f>H13-J13*3</f>
+        <v/>
+      </c>
+      <c r="T13" s="3">
+        <f>H13-J13*6</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2223,6 +5463,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>chloroform</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate)</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in chloroform-d (test1)</t>
+        </is>
+      </c>
+      <c r="S14" s="3">
+        <f>H14-J14*3</f>
+        <v/>
+      </c>
+      <c r="T14" s="3">
+        <f>H14-J14*6</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2277,6 +5543,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>chloroform-d</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in benzene-d6 (test1)</t>
+        </is>
+      </c>
+      <c r="S15" s="3">
+        <f>H15-J15*3</f>
+        <v/>
+      </c>
+      <c r="T15" s="3">
+        <f>H15-J15*6</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2331,6 +5623,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>chloroform-d</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in dichloromethane (test1)</t>
+        </is>
+      </c>
+      <c r="S16" s="3">
+        <f>H16-J16*3</f>
+        <v/>
+      </c>
+      <c r="T16" s="3">
+        <f>H16-J16*6</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2385,6 +5703,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>chloroform-d</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in dimethyl sulfoxide (test1)</t>
+        </is>
+      </c>
+      <c r="S17" s="3">
+        <f>H17-J17*3</f>
+        <v/>
+      </c>
+      <c r="T17" s="3">
+        <f>H17-J17*6</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2439,6 +5783,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>deuterium oxide</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>dextran</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in benzene (test5)</t>
+        </is>
+      </c>
+      <c r="S18" s="3">
+        <f>H18-J18*3</f>
+        <v/>
+      </c>
+      <c r="T18" s="3">
+        <f>H18-J18*6</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2493,6 +5863,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>deuterium oxide</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in toluene (test5)</t>
+        </is>
+      </c>
+      <c r="S19" s="3">
+        <f>H19-J19*3</f>
+        <v/>
+      </c>
+      <c r="T19" s="3">
+        <f>H19-J19*6</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2547,6 +5943,19 @@
           <t>polymer_name</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>deuterium oxide</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>pullulane</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2601,6 +6010,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>dichloromethane</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>dextran in deuterium oxide (test5)</t>
+        </is>
+      </c>
+      <c r="S21" s="3">
+        <f>H21-J21*3</f>
+        <v/>
+      </c>
+      <c r="T21" s="3">
+        <f>H21-J21*6</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2655,6 +6090,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>dichloromethane</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>pullulane in deuterium oxide (test5)</t>
+        </is>
+      </c>
+      <c r="S22" s="3">
+        <f>H22-J22*3</f>
+        <v/>
+      </c>
+      <c r="T22" s="3">
+        <f>H22-J22*6</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2709,6 +6170,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>dimethyl sulfoxide</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in deuterium oxide (test5)</t>
+        </is>
+      </c>
+      <c r="S23" s="3">
+        <f>H23-J23*3</f>
+        <v/>
+      </c>
+      <c r="T23" s="3">
+        <f>H23-J23*6</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2763,6 +6250,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>methanol-d4</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in benzene-d6 (test5)</t>
+        </is>
+      </c>
+      <c r="S24" s="3">
+        <f>H24-J24*3</f>
+        <v/>
+      </c>
+      <c r="T24" s="3">
+        <f>H24-J24*6</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2817,6 +6330,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in chloroform-d (test5)</t>
+        </is>
+      </c>
+      <c r="S25" s="3">
+        <f>H25-J25*3</f>
+        <v/>
+      </c>
+      <c r="T25" s="3">
+        <f>H25-J25*6</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2871,6 +6410,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide)</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in acetone-d6 (test5)</t>
+        </is>
+      </c>
+      <c r="S26" s="3">
+        <f>H26-J26*3</f>
+        <v/>
+      </c>
+      <c r="T26" s="3">
+        <f>H26-J26*6</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2925,6 +6490,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in toluene-d8 (test5)</t>
+        </is>
+      </c>
+      <c r="S27" s="3">
+        <f>H27-J27*3</f>
+        <v/>
+      </c>
+      <c r="T27" s="3">
+        <f>H27-J27*6</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2979,6 +6570,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>tetrahydrofuran-d8</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene in tetrahydrofuran-d8 (test5)</t>
+        </is>
+      </c>
+      <c r="S28" s="3">
+        <f>H28-J28*3</f>
+        <v/>
+      </c>
+      <c r="T28" s="3">
+        <f>H28-J28*6</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3033,6 +6650,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>toluene</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate)</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in deuterium oxide (test5)</t>
+        </is>
+      </c>
+      <c r="S29" s="3">
+        <f>H29-J29*3</f>
+        <v/>
+      </c>
+      <c r="T29" s="3">
+        <f>H29-J29*6</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3087,6 +6730,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>toluene-d8</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>polystyrene</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in methanol-d4 (test5)</t>
+        </is>
+      </c>
+      <c r="S30" s="3">
+        <f>H30-J30*3</f>
+        <v/>
+      </c>
+      <c r="T30" s="3">
+        <f>H30-J30*6</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3141,6 +6810,32 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene glycol) methyl ether acrylate</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in acetone-d6 (test5)</t>
+        </is>
+      </c>
+      <c r="S31" s="3">
+        <f>H31-J31*3</f>
+        <v/>
+      </c>
+      <c r="T31" s="3">
+        <f>H31-J31*6</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3195,6 +6890,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in tetrahydrofuran-d8 (test5)</t>
+        </is>
+      </c>
+      <c r="S32" s="3">
+        <f>H32-J32*3</f>
+        <v/>
+      </c>
+      <c r="T32" s="3">
+        <f>H32-J32*6</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3249,6 +6957,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in tetrahydrofuran-d8 (test5)</t>
+        </is>
+      </c>
+      <c r="S33" s="3">
+        <f>H33-J33*3</f>
+        <v/>
+      </c>
+      <c r="T33" s="3">
+        <f>H33-J33*6</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3303,6 +7024,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in chloroform-d (test5)</t>
+        </is>
+      </c>
+      <c r="S34" s="3">
+        <f>H34-J34*3</f>
+        <v/>
+      </c>
+      <c r="T34" s="3">
+        <f>H34-J34*6</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3357,6 +7091,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene oxide) in acetonitrile-d3 (test5)</t>
+        </is>
+      </c>
+      <c r="S35" s="3">
+        <f>H35-J35*3</f>
+        <v/>
+      </c>
+      <c r="T35" s="3">
+        <f>H35-J35*6</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3411,6 +7158,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in toluene (test7)</t>
+        </is>
+      </c>
+      <c r="S36" s="3">
+        <f>H36-J36*3</f>
+        <v/>
+      </c>
+      <c r="T36" s="3">
+        <f>H36-J36*6</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3465,6 +7225,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in benzene (test7)</t>
+        </is>
+      </c>
+      <c r="S37" s="3">
+        <f>H37-J37*3</f>
+        <v/>
+      </c>
+      <c r="T37" s="3">
+        <f>H37-J37*6</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3519,6 +7292,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in acetone (test7)</t>
+        </is>
+      </c>
+      <c r="S38" s="3">
+        <f>H38-J38*3</f>
+        <v/>
+      </c>
+      <c r="T38" s="3">
+        <f>H38-J38*6</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3573,6 +7359,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate) in tetrahydrofuran (test7)</t>
+        </is>
+      </c>
+      <c r="S39" s="3">
+        <f>H39-J39*3</f>
+        <v/>
+      </c>
+      <c r="T39" s="3">
+        <f>H39-J39*6</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3681,6 +7480,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate) in benzene (test7)</t>
+        </is>
+      </c>
+      <c r="S41" s="3">
+        <f>H41-J41*3</f>
+        <v/>
+      </c>
+      <c r="T41" s="3">
+        <f>H41-J41*6</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3735,6 +7547,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate) in acetone (test7)</t>
+        </is>
+      </c>
+      <c r="S42" s="3">
+        <f>H42-J42*3</f>
+        <v/>
+      </c>
+      <c r="T42" s="3">
+        <f>H42-J42*6</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3789,6 +7614,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>poly(butyl acrylate) in chloroform (test7)</t>
+        </is>
+      </c>
+      <c r="S43" s="3">
+        <f>H43-J43*3</f>
+        <v/>
+      </c>
+      <c r="T43" s="3">
+        <f>H43-J43*6</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3897,6 +7735,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene glycol) methyl ether acrylate in water (test7)</t>
+        </is>
+      </c>
+      <c r="S45" s="3">
+        <f>H45-J45*3</f>
+        <v/>
+      </c>
+      <c r="T45" s="3">
+        <f>H45-J45*6</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3951,6 +7802,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>poly(ethylene glycol) methyl ether acrylate in acetone (test7)</t>
+        </is>
+      </c>
+      <c r="S46" s="3">
+        <f>H46-J46*3</f>
+        <v/>
+      </c>
+      <c r="T46" s="3">
+        <f>H46-J46*6</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4059,9 +7923,23 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>poly(methyl methacrylate-block-poly(ethylene glycol) methyl ether methacrylate) in acetone-d6 (test7)</t>
+        </is>
+      </c>
+      <c r="S48" s="3">
+        <f>H48-J48*3</f>
+        <v/>
+      </c>
+      <c r="T48" s="3">
+        <f>H48-J48*6</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4219,1100 +8097,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="82" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Solvent</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Polymer</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>c Values</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>v Values</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>acetone</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>poly(butyl acrylate)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>[-7.56]</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>[0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>acetone</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene glycol) methyl ether acrylate</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>[-8.01]</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>[0.39]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>acetone</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>[-7.74]</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>[0.44]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>acetone-d6</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>[-7.673502333065918, -7.94]</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>[0.474477, 0.41]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>acetone-d6</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate-block-poly(ethylene glycol) methyl ether methacrylate)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>[-7.797]</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>[0.4355]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>acetone-d6</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>[-7.679147780168245, -7.78]</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>[0.452089, 0.43]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>acetonitrile-d3</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>[-7.590203777049215, -7.88]</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>[0.515853, 0.44]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>benzene</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>poly(butyl acrylate)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>[-7.83]</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>[0.51]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>benzene</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>[-7.91]</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>[0.48]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>benzene</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>[-7.7]</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>[0.54]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>benzene-d6</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>[-7.683956229316216]</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>[0.530394]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>benzene-d6</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>[-7.718505297869414, -7.94]</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>[0.5283, 0.49]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>chloroform</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>poly(butyl acrylate)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>[-7.86]</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>[0.5]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>chloroform-d</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide)</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>[-8.04]</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>[0.45]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>chloroform-d</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>[-7.579851091223765]</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>[0.543219]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>chloroform-d</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>[-7.630222150689829, -7.97]</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>[0.534677, 0.46]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>deuterium oxide</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>dextran</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>[-8.14]</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>[0.47]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>deuterium oxide</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide)</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>[-8.101177771017927, -8.39, -8.23]</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>[0.512155, 0.47, 0.49]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>deuterium oxide</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>pullulane</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>[-8.2]</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>[0.49]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>dichloromethane</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>[-7.48967889681907]</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>[0.53678]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>dichloromethane</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>[-7.56166654250548]</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>[0.521453]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>dimethyl sulfoxide</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>[-8.505773029599105]</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>[0.444236]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>methanol-d4</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide)</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>[-7.843617451027789, -8.06]</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>[0.504105, 0.45]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>tetrahydrofuran</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>[-8.02]</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>[0.43]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>tetrahydrofuran-d8</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>[-7.733838887780599, -7.94, -8.04]</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>[0.513725, 0.46, 0.45]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>tetrahydrofuran-d8</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>[-7.61465473895388]</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>[0.517608]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>tetrahydrofuran-d8</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>[-7.655839673984551, -8.07]</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>[0.519361, 0.42]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>toluene</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>[-7.72, -8.11]</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>[0.5, 0.43]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>toluene-d8</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>[-7.6700776226075575, -7.82]</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>[0.531065, 0.51]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene glycol) methyl ether acrylate</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>[-8.31]</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>[0.47]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Solvent</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Polymer</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>K Values</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>a Values</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>acetone-d6</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>[0.06862]</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>[0.56535]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>acetone-d6</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>[0.07135]</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>[0.49819]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>acetonitrile-d3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>[0.02456]</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>[0.68948]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>benzene-d6</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>[0.00848]</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>[0.7331]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>benzene-d6</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>[0.01077]</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>[0.72682]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>chloroform-d</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>[0.00517]</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>[0.77158]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>chloroform-d</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>[0.00732]</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>[0.74596]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>deuterium oxide</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>[0.02554]</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>[0.67839]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>dichloromethane</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>[0.00702]</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>[0.75226]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>dichloromethane</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>[0.01155]</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>[0.70628]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>dimethyl sulfoxide</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>[0.05265]</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>[0.47463]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>methanol-d4</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide)</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>[0.03563]</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>[0.65424]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>tetrahydrofuran-d8</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>[0.02417]</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>[0.6831]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>tetrahydrofuran-d8</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate)</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>[0.01061]</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>[0.69474]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>tetrahydrofuran-d8</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>[0.0141]</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>[0.7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>toluene-d8</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>[0.0098]</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>[0.73512]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/reports/combined_data.xlsx
+++ b/reports/combined_data.xlsx
@@ -79,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -88,6 +88,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -192,9 +195,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R2</f>
-            </strRef>
+            <v>polystyrene in tetrahydrofuran-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -214,12 +215,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$2:$T$2</f>
+              <f>'Mark-Houwink'!$M$2:$N$2</f>
             </numRef>
           </val>
         </ser>
@@ -227,9 +228,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R3</f>
-            </strRef>
+            <v>polystyrene in chloroform-d</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -249,12 +248,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$3:$T$3</f>
+              <f>'Mark-Houwink'!$M$3:$N$3</f>
             </numRef>
           </val>
         </ser>
@@ -262,9 +261,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R4</f>
-            </strRef>
+            <v>polystyrene in benzene-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -284,12 +281,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$4:$T$4</f>
+              <f>'Mark-Houwink'!$M$4:$N$4</f>
             </numRef>
           </val>
         </ser>
@@ -297,9 +294,7 @@
           <idx val="3"/>
           <order val="3"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R5</f>
-            </strRef>
+            <v>polystyrene in toluene-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -319,12 +314,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$5:$T$5</f>
+              <f>'Mark-Houwink'!$M$5:$N$5</f>
             </numRef>
           </val>
         </ser>
@@ -332,9 +327,7 @@
           <idx val="4"/>
           <order val="4"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R6</f>
-            </strRef>
+            <v>polystyrene in dichloromethane</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -354,12 +347,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$6:$T$6</f>
+              <f>'Mark-Houwink'!$M$6:$N$6</f>
             </numRef>
           </val>
         </ser>
@@ -367,9 +360,7 @@
           <idx val="5"/>
           <order val="5"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R7</f>
-            </strRef>
+            <v>polystyrene in acetone-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -389,12 +380,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$7:$T$7</f>
+              <f>'Mark-Houwink'!$M$7:$N$7</f>
             </numRef>
           </val>
         </ser>
@@ -402,9 +393,7 @@
           <idx val="6"/>
           <order val="6"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R8</f>
-            </strRef>
+            <v>poly(ethylene oxide) in methanol-d4</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -424,12 +413,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$8:$T$8</f>
+              <f>'Mark-Houwink'!$M$8:$N$8</f>
             </numRef>
           </val>
         </ser>
@@ -437,9 +426,7 @@
           <idx val="7"/>
           <order val="7"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R9</f>
-            </strRef>
+            <v>poly(ethylene oxide) in deuterium oxide</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -459,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$9:$T$9</f>
+              <f>'Mark-Houwink'!$M$9:$N$9</f>
             </numRef>
           </val>
         </ser>
@@ -472,9 +459,7 @@
           <idx val="8"/>
           <order val="8"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R10</f>
-            </strRef>
+            <v>poly(ethylene oxide) in tetrahydrofuran-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -494,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$10:$T$10</f>
+              <f>'Mark-Houwink'!$M$10:$N$10</f>
             </numRef>
           </val>
         </ser>
@@ -507,9 +492,7 @@
           <idx val="9"/>
           <order val="9"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R11</f>
-            </strRef>
+            <v>poly(ethylene oxide) in acetonitrile-d3</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -529,12 +512,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$11:$T$11</f>
+              <f>'Mark-Houwink'!$M$11:$N$11</f>
             </numRef>
           </val>
         </ser>
@@ -542,9 +525,7 @@
           <idx val="10"/>
           <order val="10"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R12</f>
-            </strRef>
+            <v>poly(ethylene oxide) in acetone-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -564,12 +545,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$12:$T$12</f>
+              <f>'Mark-Houwink'!$M$12:$N$12</f>
             </numRef>
           </val>
         </ser>
@@ -577,9 +558,7 @@
           <idx val="11"/>
           <order val="11"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R13</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in tetrahydrofuran-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -599,12 +578,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$13:$T$13</f>
+              <f>'Mark-Houwink'!$M$13:$N$13</f>
             </numRef>
           </val>
         </ser>
@@ -612,9 +591,7 @@
           <idx val="12"/>
           <order val="12"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R14</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in chloroform-d</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -634,12 +611,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$14:$T$14</f>
+              <f>'Mark-Houwink'!$M$14:$N$14</f>
             </numRef>
           </val>
         </ser>
@@ -647,9 +624,7 @@
           <idx val="13"/>
           <order val="13"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R15</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in benzene-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -669,12 +644,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$15:$T$15</f>
+              <f>'Mark-Houwink'!$M$15:$N$15</f>
             </numRef>
           </val>
         </ser>
@@ -682,9 +657,7 @@
           <idx val="14"/>
           <order val="14"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R16</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in dichloromethane</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -704,12 +677,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$16:$T$16</f>
+              <f>'Mark-Houwink'!$M$16:$N$16</f>
             </numRef>
           </val>
         </ser>
@@ -717,9 +690,7 @@
           <idx val="15"/>
           <order val="15"/>
           <tx>
-            <strRef>
-              <f>'Mark-Houwink'!R17</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in dimethyl sulfoxide</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -739,12 +710,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Mark-Houwink'!$S$1:$T$1</f>
+              <f>'Mark-Houwink'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Mark-Houwink'!$S$17:$T$17</f>
+              <f>'Mark-Houwink'!$M$17:$N$17</f>
             </numRef>
           </val>
         </ser>
@@ -845,9 +816,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R2</f>
-            </strRef>
+            <v>polystyrene in tetrahydrofuran-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -867,12 +836,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$2:$T$2</f>
+              <f>'Flory'!$M$2:$N$2</f>
             </numRef>
           </val>
         </ser>
@@ -880,9 +849,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R3</f>
-            </strRef>
+            <v>polystyrene in chloroform-d</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -902,12 +869,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$3:$T$3</f>
+              <f>'Flory'!$M$3:$N$3</f>
             </numRef>
           </val>
         </ser>
@@ -915,9 +882,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R4</f>
-            </strRef>
+            <v>polystyrene in benzene-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -937,12 +902,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$4:$T$4</f>
+              <f>'Flory'!$M$4:$N$4</f>
             </numRef>
           </val>
         </ser>
@@ -950,9 +915,7 @@
           <idx val="3"/>
           <order val="3"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R5</f>
-            </strRef>
+            <v>polystyrene in toluene-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -972,12 +935,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$5:$T$5</f>
+              <f>'Flory'!$M$5:$N$5</f>
             </numRef>
           </val>
         </ser>
@@ -985,9 +948,7 @@
           <idx val="4"/>
           <order val="4"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R6</f>
-            </strRef>
+            <v>polystyrene in dichloromethane</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1007,12 +968,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$6:$T$6</f>
+              <f>'Flory'!$M$6:$N$6</f>
             </numRef>
           </val>
         </ser>
@@ -1020,9 +981,7 @@
           <idx val="5"/>
           <order val="5"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R7</f>
-            </strRef>
+            <v>polystyrene in acetone-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1042,12 +1001,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$7:$T$7</f>
+              <f>'Flory'!$M$7:$N$7</f>
             </numRef>
           </val>
         </ser>
@@ -1055,9 +1014,7 @@
           <idx val="6"/>
           <order val="6"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R8</f>
-            </strRef>
+            <v>poly(ethylene oxide) in methanol-d4</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1077,12 +1034,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$8:$T$8</f>
+              <f>'Flory'!$M$8:$N$8</f>
             </numRef>
           </val>
         </ser>
@@ -1090,9 +1047,7 @@
           <idx val="7"/>
           <order val="7"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R9</f>
-            </strRef>
+            <v>poly(ethylene oxide) in deuterium oxide</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1112,12 +1067,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$9:$T$9</f>
+              <f>'Flory'!$M$9:$N$9</f>
             </numRef>
           </val>
         </ser>
@@ -1125,9 +1080,7 @@
           <idx val="8"/>
           <order val="8"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R10</f>
-            </strRef>
+            <v>poly(ethylene oxide) in tetrahydrofuran-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1147,12 +1100,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$10:$T$10</f>
+              <f>'Flory'!$M$10:$N$10</f>
             </numRef>
           </val>
         </ser>
@@ -1160,9 +1113,7 @@
           <idx val="9"/>
           <order val="9"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R11</f>
-            </strRef>
+            <v>poly(ethylene oxide) in acetonitrile-d3</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1182,12 +1133,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$11:$T$11</f>
+              <f>'Flory'!$M$11:$N$11</f>
             </numRef>
           </val>
         </ser>
@@ -1195,9 +1146,7 @@
           <idx val="10"/>
           <order val="10"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R12</f>
-            </strRef>
+            <v>poly(ethylene oxide) in acetone-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1217,12 +1166,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$12:$T$12</f>
+              <f>'Flory'!$M$12:$N$12</f>
             </numRef>
           </val>
         </ser>
@@ -1230,9 +1179,7 @@
           <idx val="11"/>
           <order val="11"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R13</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in tetrahydrofuran-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1252,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$13:$T$13</f>
+              <f>'Flory'!$M$13:$N$13</f>
             </numRef>
           </val>
         </ser>
@@ -1265,9 +1212,7 @@
           <idx val="12"/>
           <order val="12"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R14</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in chloroform-d</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1287,12 +1232,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$14:$T$14</f>
+              <f>'Flory'!$M$14:$N$14</f>
             </numRef>
           </val>
         </ser>
@@ -1300,9 +1245,7 @@
           <idx val="13"/>
           <order val="13"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R15</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in benzene-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1322,12 +1265,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$15:$T$15</f>
+              <f>'Flory'!$M$15:$N$15</f>
             </numRef>
           </val>
         </ser>
@@ -1335,9 +1278,7 @@
           <idx val="14"/>
           <order val="14"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R16</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in dichloromethane</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1357,12 +1298,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$16:$T$16</f>
+              <f>'Flory'!$M$16:$N$16</f>
             </numRef>
           </val>
         </ser>
@@ -1370,9 +1311,7 @@
           <idx val="15"/>
           <order val="15"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R17</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in dimethyl sulfoxide</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1392,12 +1331,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$17:$T$17</f>
+              <f>'Flory'!$M$17:$N$17</f>
             </numRef>
           </val>
         </ser>
@@ -1405,9 +1344,7 @@
           <idx val="16"/>
           <order val="16"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R18</f>
-            </strRef>
+            <v>polystyrene in benzene</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1427,12 +1364,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$18:$T$18</f>
+              <f>'Flory'!$M$18:$N$18</f>
             </numRef>
           </val>
         </ser>
@@ -1440,9 +1377,7 @@
           <idx val="17"/>
           <order val="17"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R19</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in toluene</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1462,12 +1397,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$19:$T$19</f>
+              <f>'Flory'!$M$19:$N$19</f>
             </numRef>
           </val>
         </ser>
@@ -1475,9 +1410,7 @@
           <idx val="18"/>
           <order val="18"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R20</f>
-            </strRef>
+            <v>dextran in deuterium oxide</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1497,12 +1430,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$20:$T$20</f>
+              <f>'Flory'!$M$21:$N$21</f>
             </numRef>
           </val>
         </ser>
@@ -1510,9 +1443,7 @@
           <idx val="19"/>
           <order val="19"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R21</f>
-            </strRef>
+            <v>pullulane in deuterium oxide</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1532,12 +1463,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$21:$T$21</f>
+              <f>'Flory'!$M$22:$N$22</f>
             </numRef>
           </val>
         </ser>
@@ -1545,9 +1476,7 @@
           <idx val="20"/>
           <order val="20"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R22</f>
-            </strRef>
+            <v>poly(ethylene oxide) in deuterium oxide</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1567,12 +1496,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$22:$T$22</f>
+              <f>'Flory'!$M$23:$N$23</f>
             </numRef>
           </val>
         </ser>
@@ -1580,9 +1509,7 @@
           <idx val="21"/>
           <order val="21"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R23</f>
-            </strRef>
+            <v>polystyrene in benzene-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1602,12 +1529,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$23:$T$23</f>
+              <f>'Flory'!$M$24:$N$24</f>
             </numRef>
           </val>
         </ser>
@@ -1615,9 +1542,7 @@
           <idx val="22"/>
           <order val="22"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R24</f>
-            </strRef>
+            <v>polystyrene in chloroform-d</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1637,12 +1562,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$24:$T$24</f>
+              <f>'Flory'!$M$25:$N$25</f>
             </numRef>
           </val>
         </ser>
@@ -1650,9 +1575,7 @@
           <idx val="23"/>
           <order val="23"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R25</f>
-            </strRef>
+            <v>polystyrene in acetone-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1672,12 +1595,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$25:$T$25</f>
+              <f>'Flory'!$M$26:$N$26</f>
             </numRef>
           </val>
         </ser>
@@ -1685,9 +1608,7 @@
           <idx val="24"/>
           <order val="24"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R26</f>
-            </strRef>
+            <v>polystyrene in toluene-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1707,12 +1628,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$26:$T$26</f>
+              <f>'Flory'!$M$27:$N$27</f>
             </numRef>
           </val>
         </ser>
@@ -1720,9 +1641,7 @@
           <idx val="25"/>
           <order val="25"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R27</f>
-            </strRef>
+            <v>polystyrene in tetrahydrofuran-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1742,12 +1661,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$27:$T$27</f>
+              <f>'Flory'!$M$28:$N$28</f>
             </numRef>
           </val>
         </ser>
@@ -1755,9 +1674,7 @@
           <idx val="26"/>
           <order val="26"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R28</f>
-            </strRef>
+            <v>poly(ethylene oxide) in deuterium oxide</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1777,12 +1694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$28:$T$28</f>
+              <f>'Flory'!$M$29:$N$29</f>
             </numRef>
           </val>
         </ser>
@@ -1790,9 +1707,7 @@
           <idx val="27"/>
           <order val="27"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R29</f>
-            </strRef>
+            <v>poly(ethylene oxide) in methanol-d4</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1812,12 +1727,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$29:$T$29</f>
+              <f>'Flory'!$M$30:$N$30</f>
             </numRef>
           </val>
         </ser>
@@ -1825,9 +1740,7 @@
           <idx val="28"/>
           <order val="28"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R30</f>
-            </strRef>
+            <v>poly(ethylene oxide) in acetone-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1847,12 +1760,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$30:$T$30</f>
+              <f>'Flory'!$M$31:$N$31</f>
             </numRef>
           </val>
         </ser>
@@ -1860,9 +1773,7 @@
           <idx val="29"/>
           <order val="29"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R31</f>
-            </strRef>
+            <v>poly(ethylene oxide) in tetrahydrofuran-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1882,12 +1793,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$31:$T$31</f>
+              <f>'Flory'!$M$32:$N$32</f>
             </numRef>
           </val>
         </ser>
@@ -1895,9 +1806,7 @@
           <idx val="30"/>
           <order val="30"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R32</f>
-            </strRef>
+            <v>poly(ethylene oxide) in tetrahydrofuran-d8</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1917,12 +1826,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$32:$T$32</f>
+              <f>'Flory'!$M$33:$N$33</f>
             </numRef>
           </val>
         </ser>
@@ -1930,9 +1839,7 @@
           <idx val="31"/>
           <order val="31"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R33</f>
-            </strRef>
+            <v>poly(ethylene oxide) in chloroform-d</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1952,12 +1859,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$33:$T$33</f>
+              <f>'Flory'!$M$34:$N$34</f>
             </numRef>
           </val>
         </ser>
@@ -1965,9 +1872,7 @@
           <idx val="32"/>
           <order val="32"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R34</f>
-            </strRef>
+            <v>poly(ethylene oxide) in acetonitrile-d3</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1987,12 +1892,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$34:$T$34</f>
+              <f>'Flory'!$M$35:$N$35</f>
             </numRef>
           </val>
         </ser>
@@ -2000,9 +1905,7 @@
           <idx val="33"/>
           <order val="33"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R35</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in toluene</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2022,12 +1925,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$35:$T$35</f>
+              <f>'Flory'!$M$36:$N$36</f>
             </numRef>
           </val>
         </ser>
@@ -2035,9 +1938,7 @@
           <idx val="34"/>
           <order val="34"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R36</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in benzene</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2057,12 +1958,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$36:$T$36</f>
+              <f>'Flory'!$M$37:$N$37</f>
             </numRef>
           </val>
         </ser>
@@ -2070,9 +1971,7 @@
           <idx val="35"/>
           <order val="35"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R37</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in acetone</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2092,12 +1991,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$37:$T$37</f>
+              <f>'Flory'!$M$38:$N$38</f>
             </numRef>
           </val>
         </ser>
@@ -2105,9 +2004,7 @@
           <idx val="36"/>
           <order val="36"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R38</f>
-            </strRef>
+            <v>poly(methyl methacrylate) in tetrahydrofuran</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2127,12 +2024,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$38:$T$38</f>
+              <f>'Flory'!$M$39:$N$39</f>
             </numRef>
           </val>
         </ser>
@@ -2140,9 +2037,7 @@
           <idx val="37"/>
           <order val="37"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R39</f>
-            </strRef>
+            <v>poly(butyl acrylate) in benzene</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2162,12 +2057,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$39:$T$39</f>
+              <f>'Flory'!$M$41:$N$41</f>
             </numRef>
           </val>
         </ser>
@@ -2175,9 +2070,7 @@
           <idx val="38"/>
           <order val="38"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R40</f>
-            </strRef>
+            <v>poly(butyl acrylate) in acetone</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2197,12 +2090,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$40:$T$40</f>
+              <f>'Flory'!$M$42:$N$42</f>
             </numRef>
           </val>
         </ser>
@@ -2210,9 +2103,7 @@
           <idx val="39"/>
           <order val="39"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R41</f>
-            </strRef>
+            <v>poly(butyl acrylate) in chloroform</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2232,12 +2123,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$41:$T$41</f>
+              <f>'Flory'!$M$43:$N$43</f>
             </numRef>
           </val>
         </ser>
@@ -2245,9 +2136,7 @@
           <idx val="40"/>
           <order val="40"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R42</f>
-            </strRef>
+            <v>poly(ethylene glycol) methyl ether acrylate in water</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2267,12 +2156,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$42:$T$42</f>
+              <f>'Flory'!$M$45:$N$45</f>
             </numRef>
           </val>
         </ser>
@@ -2280,9 +2169,7 @@
           <idx val="41"/>
           <order val="41"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R43</f>
-            </strRef>
+            <v>poly(ethylene glycol) methyl ether acrylate in acetone</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2302,12 +2189,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$43:$T$43</f>
+              <f>'Flory'!$M$46:$N$46</f>
             </numRef>
           </val>
         </ser>
@@ -2315,9 +2202,7 @@
           <idx val="42"/>
           <order val="42"/>
           <tx>
-            <strRef>
-              <f>'Flory'!R44</f>
-            </strRef>
+            <v>poly(methyl methacrylate-block-poly(ethylene glycol) methyl ether methacrylate) in acetone-d6</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2337,152 +2222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
+              <f>'Flory'!$M$1:$N$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Flory'!$S$44:$T$44</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="43"/>
-          <order val="43"/>
-          <tx>
-            <strRef>
-              <f>'Flory'!R45</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Flory'!$S$45:$T$45</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="44"/>
-          <order val="44"/>
-          <tx>
-            <strRef>
-              <f>'Flory'!R46</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Flory'!$S$46:$T$46</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="45"/>
-          <order val="45"/>
-          <tx>
-            <strRef>
-              <f>'Flory'!R47</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="1F497D"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Flory'!$S$47:$T$47</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="46"/>
-          <order val="46"/>
-          <tx>
-            <strRef>
-              <f>'Flory'!R48</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="C0504D"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Flory'!$S$1:$T$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Flory'!$S$48:$T$48</f>
+              <f>'Flory'!$M$48:$N$48</f>
             </numRef>
           </val>
         </ser>
@@ -2561,7 +2306,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>19</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -2588,7 +2333,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>19</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -2900,7 +2645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2915,14 +2660,12 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="58" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2986,31 +2729,26 @@
           <t>Failed Field</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Solvent</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Polymer</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Series</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="T1" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="2">
@@ -3068,31 +2806,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="M2" s="3">
+        <f>LOG10(H2)+J2*3</f>
+        <v/>
+      </c>
+      <c r="N2" s="3">
+        <f>LOG10(H2)+J2*6</f>
+        <v/>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>acetone-d6</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene oxide)</t>
         </is>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in tetrahydrofuran-d8 (test1)</t>
-        </is>
-      </c>
-      <c r="S2" s="3">
-        <f>LOG10(H2)+J2*3</f>
-        <v/>
-      </c>
-      <c r="T2" s="3">
-        <f>LOG10(H2)+J2*6</f>
-        <v/>
       </c>
     </row>
     <row r="3">
@@ -3150,31 +2883,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="M3" s="3">
+        <f>LOG10(H3)+J3*3</f>
+        <v/>
+      </c>
+      <c r="N3" s="3">
+        <f>LOG10(H3)+J3*6</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>acetone-d6</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in chloroform-d (test1)</t>
-        </is>
-      </c>
-      <c r="S3" s="3">
-        <f>LOG10(H3)+J3*3</f>
-        <v/>
-      </c>
-      <c r="T3" s="3">
-        <f>LOG10(H3)+J3*6</f>
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -3232,31 +2960,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="3">
+        <f>LOG10(H4)+J4*3</f>
+        <v/>
+      </c>
+      <c r="N4" s="3">
+        <f>LOG10(H4)+J4*6</f>
+        <v/>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>acetonitrile-d3</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene oxide)</t>
         </is>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in benzene-d6 (test1)</t>
-        </is>
-      </c>
-      <c r="S4" s="3">
-        <f>LOG10(H4)+J4*3</f>
-        <v/>
-      </c>
-      <c r="T4" s="3">
-        <f>LOG10(H4)+J4*6</f>
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -3314,31 +3037,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="3">
+        <f>LOG10(H5)+J5*3</f>
+        <v/>
+      </c>
+      <c r="N5" s="3">
+        <f>LOG10(H5)+J5*6</f>
+        <v/>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>benzene-d6</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in toluene-d8 (test1)</t>
-        </is>
-      </c>
-      <c r="S5" s="3">
-        <f>LOG10(H5)+J5*3</f>
-        <v/>
-      </c>
-      <c r="T5" s="3">
-        <f>LOG10(H5)+J5*6</f>
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -3396,31 +3114,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="M6" s="3">
+        <f>LOG10(H6)+J6*3</f>
+        <v/>
+      </c>
+      <c r="N6" s="3">
+        <f>LOG10(H6)+J6*6</f>
+        <v/>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>benzene-d6</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in dichloromethane (test1)</t>
-        </is>
-      </c>
-      <c r="S6" s="3">
-        <f>LOG10(H6)+J6*3</f>
-        <v/>
-      </c>
-      <c r="T6" s="3">
-        <f>LOG10(H6)+J6*6</f>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -3478,31 +3191,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M7" s="3">
+        <f>LOG10(H7)+J7*3</f>
+        <v/>
+      </c>
+      <c r="N7" s="3">
+        <f>LOG10(H7)+J7*6</f>
+        <v/>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>chloroform-d</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in acetone-d6 (test1)</t>
-        </is>
-      </c>
-      <c r="S7" s="3">
-        <f>LOG10(H7)+J7*3</f>
-        <v/>
-      </c>
-      <c r="T7" s="3">
-        <f>LOG10(H7)+J7*6</f>
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -3560,31 +3268,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="3">
+        <f>LOG10(H8)+J8*3</f>
+        <v/>
+      </c>
+      <c r="N8" s="3">
+        <f>LOG10(H8)+J8*6</f>
+        <v/>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>chloroform-d</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in methanol-d4 (test1)</t>
-        </is>
-      </c>
-      <c r="S8" s="3">
-        <f>LOG10(H8)+J8*3</f>
-        <v/>
-      </c>
-      <c r="T8" s="3">
-        <f>LOG10(H8)+J8*6</f>
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -3642,31 +3345,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="M9" s="3">
+        <f>LOG10(H9)+J9*3</f>
+        <v/>
+      </c>
+      <c r="N9" s="3">
+        <f>LOG10(H9)+J9*6</f>
+        <v/>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>deuterium oxide</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene oxide)</t>
         </is>
       </c>
-      <c r="P9" s="3" t="n">
+      <c r="R9" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in deuterium oxide (test1)</t>
-        </is>
-      </c>
-      <c r="S9" s="3">
-        <f>LOG10(H9)+J9*3</f>
-        <v/>
-      </c>
-      <c r="T9" s="3">
-        <f>LOG10(H9)+J9*6</f>
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -3724,31 +3422,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="M10" s="3">
+        <f>LOG10(H10)+J10*3</f>
+        <v/>
+      </c>
+      <c r="N10" s="3">
+        <f>LOG10(H10)+J10*6</f>
+        <v/>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>dichloromethane</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P10" s="3" t="n">
+      <c r="R10" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in tetrahydrofuran-d8 (test1)</t>
-        </is>
-      </c>
-      <c r="S10" s="3">
-        <f>LOG10(H10)+J10*3</f>
-        <v/>
-      </c>
-      <c r="T10" s="3">
-        <f>LOG10(H10)+J10*6</f>
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -3806,31 +3499,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="3">
+        <f>LOG10(H11)+J11*3</f>
+        <v/>
+      </c>
+      <c r="N11" s="3">
+        <f>LOG10(H11)+J11*6</f>
+        <v/>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>dichloromethane</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P11" s="3" t="n">
+      <c r="R11" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in acetonitrile-d3 (test1)</t>
-        </is>
-      </c>
-      <c r="S11" s="3">
-        <f>LOG10(H11)+J11*3</f>
-        <v/>
-      </c>
-      <c r="T11" s="3">
-        <f>LOG10(H11)+J11*6</f>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -3888,31 +3576,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="M12" s="3">
+        <f>LOG10(H12)+J12*3</f>
+        <v/>
+      </c>
+      <c r="N12" s="3">
+        <f>LOG10(H12)+J12*6</f>
+        <v/>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>dimethyl sulfoxide</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P12" s="3" t="n">
+      <c r="R12" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in acetone-d6 (test1)</t>
-        </is>
-      </c>
-      <c r="S12" s="3">
-        <f>LOG10(H12)+J12*3</f>
-        <v/>
-      </c>
-      <c r="T12" s="3">
-        <f>LOG10(H12)+J12*6</f>
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -3970,31 +3653,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="3">
+        <f>LOG10(H13)+J13*3</f>
+        <v/>
+      </c>
+      <c r="N13" s="3">
+        <f>LOG10(H13)+J13*6</f>
+        <v/>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>methanol-d4</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene oxide)</t>
         </is>
       </c>
-      <c r="P13" s="3" t="n">
+      <c r="R13" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in tetrahydrofuran-d8 (test1)</t>
-        </is>
-      </c>
-      <c r="S13" s="3">
-        <f>LOG10(H13)+J13*3</f>
-        <v/>
-      </c>
-      <c r="T13" s="3">
-        <f>LOG10(H13)+J13*6</f>
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -4052,31 +3730,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="M14" s="3">
+        <f>LOG10(H14)+J14*3</f>
+        <v/>
+      </c>
+      <c r="N14" s="3">
+        <f>LOG10(H14)+J14*6</f>
+        <v/>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>tetrahydrofuran-d8</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene oxide)</t>
         </is>
       </c>
-      <c r="P14" s="3" t="n">
+      <c r="R14" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in chloroform-d (test1)</t>
-        </is>
-      </c>
-      <c r="S14" s="3">
-        <f>LOG10(H14)+J14*3</f>
-        <v/>
-      </c>
-      <c r="T14" s="3">
-        <f>LOG10(H14)+J14*6</f>
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -4134,31 +3807,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="M15" s="3">
+        <f>LOG10(H15)+J15*3</f>
+        <v/>
+      </c>
+      <c r="N15" s="3">
+        <f>LOG10(H15)+J15*6</f>
+        <v/>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>tetrahydrofuran-d8</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P15" s="3" t="n">
+      <c r="R15" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in benzene-d6 (test1)</t>
-        </is>
-      </c>
-      <c r="S15" s="3">
-        <f>LOG10(H15)+J15*3</f>
-        <v/>
-      </c>
-      <c r="T15" s="3">
-        <f>LOG10(H15)+J15*6</f>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -4216,31 +3884,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="M16" s="3">
+        <f>LOG10(H16)+J16*3</f>
+        <v/>
+      </c>
+      <c r="N16" s="3">
+        <f>LOG10(H16)+J16*6</f>
+        <v/>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>tetrahydrofuran-d8</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P16" s="3" t="n">
+      <c r="R16" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in dichloromethane (test1)</t>
-        </is>
-      </c>
-      <c r="S16" s="3">
-        <f>LOG10(H16)+J16*3</f>
-        <v/>
-      </c>
-      <c r="T16" s="3">
-        <f>LOG10(H16)+J16*6</f>
-        <v/>
       </c>
     </row>
     <row r="17">
@@ -4298,31 +3961,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="M17" s="3">
+        <f>LOG10(H17)+J17*3</f>
+        <v/>
+      </c>
+      <c r="N17" s="3">
+        <f>LOG10(H17)+J17*6</f>
+        <v/>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>toluene-d8</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P17" s="3" t="n">
+      <c r="R17" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in dimethyl sulfoxide (test1)</t>
-        </is>
-      </c>
-      <c r="S17" s="3">
-        <f>LOG10(H17)+J17*3</f>
-        <v/>
-      </c>
-      <c r="T17" s="3">
-        <f>LOG10(H17)+J17*6</f>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -4337,7 +3995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4352,14 +4010,12 @@
     <col width="29" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="82" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="104" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="82" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4423,31 +4079,26 @@
           <t>Failed Field</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Solvent</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Polymer</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Series</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="T1" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="2">
@@ -4503,31 +4154,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="M2" s="3">
+        <f>H2-J2*3</f>
+        <v/>
+      </c>
+      <c r="N2" s="3">
+        <f>H2-J2*6</f>
+        <v/>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>acetone</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>poly(butyl acrylate)</t>
         </is>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in tetrahydrofuran-d8 (test1)</t>
-        </is>
-      </c>
-      <c r="S2" s="3">
-        <f>H2-J2*3</f>
-        <v/>
-      </c>
-      <c r="T2" s="3">
-        <f>H2-J2*6</f>
-        <v/>
       </c>
     </row>
     <row r="3">
@@ -4583,31 +4229,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="M3" s="3">
+        <f>H3-J3*3</f>
+        <v/>
+      </c>
+      <c r="N3" s="3">
+        <f>H3-J3*6</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>acetone</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene glycol) methyl ether acrylate</t>
         </is>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in chloroform-d (test1)</t>
-        </is>
-      </c>
-      <c r="S3" s="3">
-        <f>H3-J3*3</f>
-        <v/>
-      </c>
-      <c r="T3" s="3">
-        <f>H3-J3*6</f>
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -4663,31 +4304,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="3">
+        <f>H4-J4*3</f>
+        <v/>
+      </c>
+      <c r="N4" s="3">
+        <f>H4-J4*6</f>
+        <v/>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>acetone</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in benzene-d6 (test1)</t>
-        </is>
-      </c>
-      <c r="S4" s="3">
-        <f>H4-J4*3</f>
-        <v/>
-      </c>
-      <c r="T4" s="3">
-        <f>H4-J4*6</f>
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -4743,31 +4379,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="3">
+        <f>H5-J5*3</f>
+        <v/>
+      </c>
+      <c r="N5" s="3">
+        <f>H5-J5*6</f>
+        <v/>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>acetone-d6</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene oxide)</t>
         </is>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in toluene-d8 (test1)</t>
-        </is>
-      </c>
-      <c r="S5" s="3">
-        <f>H5-J5*3</f>
-        <v/>
-      </c>
-      <c r="T5" s="3">
-        <f>H5-J5*6</f>
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -4823,31 +4454,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="M6" s="3">
+        <f>H6-J6*3</f>
+        <v/>
+      </c>
+      <c r="N6" s="3">
+        <f>H6-J6*6</f>
+        <v/>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>acetone-d6</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate-block-poly(ethylene glycol) methyl ether methacrylate)</t>
         </is>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in dichloromethane (test1)</t>
-        </is>
-      </c>
-      <c r="S6" s="3">
-        <f>H6-J6*3</f>
-        <v/>
-      </c>
-      <c r="T6" s="3">
-        <f>H6-J6*6</f>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -4903,31 +4529,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M7" s="3">
+        <f>H7-J7*3</f>
+        <v/>
+      </c>
+      <c r="N7" s="3">
+        <f>H7-J7*6</f>
+        <v/>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>acetone-d6</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in acetone-d6 (test1)</t>
-        </is>
-      </c>
-      <c r="S7" s="3">
-        <f>H7-J7*3</f>
-        <v/>
-      </c>
-      <c r="T7" s="3">
-        <f>H7-J7*6</f>
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -4983,31 +4604,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="3">
+        <f>H8-J8*3</f>
+        <v/>
+      </c>
+      <c r="N8" s="3">
+        <f>H8-J8*6</f>
+        <v/>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>acetonitrile-d3</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene oxide)</t>
         </is>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in methanol-d4 (test1)</t>
-        </is>
-      </c>
-      <c r="S8" s="3">
-        <f>H8-J8*3</f>
-        <v/>
-      </c>
-      <c r="T8" s="3">
-        <f>H8-J8*6</f>
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -5063,31 +4679,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="M9" s="3">
+        <f>H9-J9*3</f>
+        <v/>
+      </c>
+      <c r="N9" s="3">
+        <f>H9-J9*6</f>
+        <v/>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>benzene</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>poly(butyl acrylate)</t>
         </is>
       </c>
-      <c r="P9" s="3" t="n">
+      <c r="R9" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in deuterium oxide (test1)</t>
-        </is>
-      </c>
-      <c r="S9" s="3">
-        <f>H9-J9*3</f>
-        <v/>
-      </c>
-      <c r="T9" s="3">
-        <f>H9-J9*6</f>
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -5143,31 +4754,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="M10" s="3">
+        <f>H10-J10*3</f>
+        <v/>
+      </c>
+      <c r="N10" s="3">
+        <f>H10-J10*6</f>
+        <v/>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>benzene</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P10" s="3" t="n">
+      <c r="R10" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in tetrahydrofuran-d8 (test1)</t>
-        </is>
-      </c>
-      <c r="S10" s="3">
-        <f>H10-J10*3</f>
-        <v/>
-      </c>
-      <c r="T10" s="3">
-        <f>H10-J10*6</f>
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -5223,31 +4829,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="3">
+        <f>H11-J11*3</f>
+        <v/>
+      </c>
+      <c r="N11" s="3">
+        <f>H11-J11*6</f>
+        <v/>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>benzene</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P11" s="3" t="n">
+      <c r="R11" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in acetonitrile-d3 (test1)</t>
-        </is>
-      </c>
-      <c r="S11" s="3">
-        <f>H11-J11*3</f>
-        <v/>
-      </c>
-      <c r="T11" s="3">
-        <f>H11-J11*6</f>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -5303,31 +4904,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="M12" s="3">
+        <f>H12-J12*3</f>
+        <v/>
+      </c>
+      <c r="N12" s="3">
+        <f>H12-J12*6</f>
+        <v/>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>benzene-d6</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P12" s="3" t="n">
+      <c r="R12" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in acetone-d6 (test1)</t>
-        </is>
-      </c>
-      <c r="S12" s="3">
-        <f>H12-J12*3</f>
-        <v/>
-      </c>
-      <c r="T12" s="3">
-        <f>H12-J12*6</f>
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -5383,31 +4979,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="3">
+        <f>H13-J13*3</f>
+        <v/>
+      </c>
+      <c r="N13" s="3">
+        <f>H13-J13*6</f>
+        <v/>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>benzene-d6</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P13" s="3" t="n">
+      <c r="R13" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in tetrahydrofuran-d8 (test1)</t>
-        </is>
-      </c>
-      <c r="S13" s="3">
-        <f>H13-J13*3</f>
-        <v/>
-      </c>
-      <c r="T13" s="3">
-        <f>H13-J13*6</f>
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -5463,31 +5054,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="M14" s="3">
+        <f>H14-J14*3</f>
+        <v/>
+      </c>
+      <c r="N14" s="3">
+        <f>H14-J14*6</f>
+        <v/>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>chloroform</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>poly(butyl acrylate)</t>
         </is>
       </c>
-      <c r="P14" s="3" t="n">
+      <c r="R14" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in chloroform-d (test1)</t>
-        </is>
-      </c>
-      <c r="S14" s="3">
-        <f>H14-J14*3</f>
-        <v/>
-      </c>
-      <c r="T14" s="3">
-        <f>H14-J14*6</f>
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -5543,31 +5129,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="M15" s="3">
+        <f>H15-J15*3</f>
+        <v/>
+      </c>
+      <c r="N15" s="3">
+        <f>H15-J15*6</f>
+        <v/>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>chloroform-d</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene oxide)</t>
         </is>
       </c>
-      <c r="P15" s="3" t="n">
+      <c r="R15" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in benzene-d6 (test1)</t>
-        </is>
-      </c>
-      <c r="S15" s="3">
-        <f>H15-J15*3</f>
-        <v/>
-      </c>
-      <c r="T15" s="3">
-        <f>H15-J15*6</f>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -5623,31 +5204,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="M16" s="3">
+        <f>H16-J16*3</f>
+        <v/>
+      </c>
+      <c r="N16" s="3">
+        <f>H16-J16*6</f>
+        <v/>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>chloroform-d</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P16" s="3" t="n">
+      <c r="R16" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in dichloromethane (test1)</t>
-        </is>
-      </c>
-      <c r="S16" s="3">
-        <f>H16-J16*3</f>
-        <v/>
-      </c>
-      <c r="T16" s="3">
-        <f>H16-J16*6</f>
-        <v/>
       </c>
     </row>
     <row r="17">
@@ -5703,31 +5279,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="M17" s="3">
+        <f>H17-J17*3</f>
+        <v/>
+      </c>
+      <c r="N17" s="3">
+        <f>H17-J17*6</f>
+        <v/>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>chloroform-d</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P17" s="3" t="n">
+      <c r="R17" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in dimethyl sulfoxide (test1)</t>
-        </is>
-      </c>
-      <c r="S17" s="3">
-        <f>H17-J17*3</f>
-        <v/>
-      </c>
-      <c r="T17" s="3">
-        <f>H17-J17*6</f>
-        <v/>
       </c>
     </row>
     <row r="18">
@@ -5783,31 +5354,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="M18" s="3">
+        <f>H18-J18*3</f>
+        <v/>
+      </c>
+      <c r="N18" s="3">
+        <f>H18-J18*6</f>
+        <v/>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>deuterium oxide</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>dextran</t>
         </is>
       </c>
-      <c r="P18" s="3" t="n">
+      <c r="R18" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in benzene (test5)</t>
-        </is>
-      </c>
-      <c r="S18" s="3">
-        <f>H18-J18*3</f>
-        <v/>
-      </c>
-      <c r="T18" s="3">
-        <f>H18-J18*6</f>
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -5863,31 +5429,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="M19" s="3">
+        <f>H19-J19*3</f>
+        <v/>
+      </c>
+      <c r="N19" s="3">
+        <f>H19-J19*6</f>
+        <v/>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>deuterium oxide</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene oxide)</t>
         </is>
       </c>
-      <c r="P19" s="3" t="n">
+      <c r="R19" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in toluene (test5)</t>
-        </is>
-      </c>
-      <c r="S19" s="3">
-        <f>H19-J19*3</f>
-        <v/>
-      </c>
-      <c r="T19" s="3">
-        <f>H19-J19*6</f>
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -5943,17 +5504,19 @@
           <t>polymer_name</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>deuterium oxide</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>pullulane</t>
         </is>
       </c>
-      <c r="P20" s="3" t="n">
+      <c r="R20" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6010,31 +5573,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="M21" s="3">
+        <f>H21-J21*3</f>
+        <v/>
+      </c>
+      <c r="N21" s="3">
+        <f>H21-J21*6</f>
+        <v/>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>dichloromethane</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P21" s="3" t="n">
+      <c r="R21" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>dextran in deuterium oxide (test5)</t>
-        </is>
-      </c>
-      <c r="S21" s="3">
-        <f>H21-J21*3</f>
-        <v/>
-      </c>
-      <c r="T21" s="3">
-        <f>H21-J21*6</f>
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -6090,31 +5648,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="M22" s="3">
+        <f>H22-J22*3</f>
+        <v/>
+      </c>
+      <c r="N22" s="3">
+        <f>H22-J22*6</f>
+        <v/>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>dichloromethane</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="R22" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>pullulane in deuterium oxide (test5)</t>
-        </is>
-      </c>
-      <c r="S22" s="3">
-        <f>H22-J22*3</f>
-        <v/>
-      </c>
-      <c r="T22" s="3">
-        <f>H22-J22*6</f>
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -6170,31 +5723,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="M23" s="3">
+        <f>H23-J23*3</f>
+        <v/>
+      </c>
+      <c r="N23" s="3">
+        <f>H23-J23*6</f>
+        <v/>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>dimethyl sulfoxide</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P23" s="3" t="n">
+      <c r="R23" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in deuterium oxide (test5)</t>
-        </is>
-      </c>
-      <c r="S23" s="3">
-        <f>H23-J23*3</f>
-        <v/>
-      </c>
-      <c r="T23" s="3">
-        <f>H23-J23*6</f>
-        <v/>
       </c>
     </row>
     <row r="24">
@@ -6250,31 +5798,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="M24" s="3">
+        <f>H24-J24*3</f>
+        <v/>
+      </c>
+      <c r="N24" s="3">
+        <f>H24-J24*6</f>
+        <v/>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>methanol-d4</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene oxide)</t>
         </is>
       </c>
-      <c r="P24" s="3" t="n">
+      <c r="R24" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in benzene-d6 (test5)</t>
-        </is>
-      </c>
-      <c r="S24" s="3">
-        <f>H24-J24*3</f>
-        <v/>
-      </c>
-      <c r="T24" s="3">
-        <f>H24-J24*6</f>
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -6330,31 +5873,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="M25" s="3">
+        <f>H25-J25*3</f>
+        <v/>
+      </c>
+      <c r="N25" s="3">
+        <f>H25-J25*6</f>
+        <v/>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>tetrahydrofuran</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P25" s="3" t="n">
+      <c r="R25" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in chloroform-d (test5)</t>
-        </is>
-      </c>
-      <c r="S25" s="3">
-        <f>H25-J25*3</f>
-        <v/>
-      </c>
-      <c r="T25" s="3">
-        <f>H25-J25*6</f>
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -6410,31 +5948,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="M26" s="3">
+        <f>H26-J26*3</f>
+        <v/>
+      </c>
+      <c r="N26" s="3">
+        <f>H26-J26*6</f>
+        <v/>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>tetrahydrofuran-d8</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene oxide)</t>
         </is>
       </c>
-      <c r="P26" s="3" t="n">
+      <c r="R26" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in acetone-d6 (test5)</t>
-        </is>
-      </c>
-      <c r="S26" s="3">
-        <f>H26-J26*3</f>
-        <v/>
-      </c>
-      <c r="T26" s="3">
-        <f>H26-J26*6</f>
-        <v/>
       </c>
     </row>
     <row r="27">
@@ -6490,31 +6023,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="M27" s="3">
+        <f>H27-J27*3</f>
+        <v/>
+      </c>
+      <c r="N27" s="3">
+        <f>H27-J27*6</f>
+        <v/>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>tetrahydrofuran-d8</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P27" s="3" t="n">
+      <c r="R27" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in toluene-d8 (test5)</t>
-        </is>
-      </c>
-      <c r="S27" s="3">
-        <f>H27-J27*3</f>
-        <v/>
-      </c>
-      <c r="T27" s="3">
-        <f>H27-J27*6</f>
-        <v/>
       </c>
     </row>
     <row r="28">
@@ -6570,31 +6098,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="M28" s="3">
+        <f>H28-J28*3</f>
+        <v/>
+      </c>
+      <c r="N28" s="3">
+        <f>H28-J28*6</f>
+        <v/>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>tetrahydrofuran-d8</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P28" s="3" t="n">
+      <c r="R28" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>polystyrene in tetrahydrofuran-d8 (test5)</t>
-        </is>
-      </c>
-      <c r="S28" s="3">
-        <f>H28-J28*3</f>
-        <v/>
-      </c>
-      <c r="T28" s="3">
-        <f>H28-J28*6</f>
-        <v/>
       </c>
     </row>
     <row r="29">
@@ -6650,31 +6173,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="M29" s="3">
+        <f>H29-J29*3</f>
+        <v/>
+      </c>
+      <c r="N29" s="3">
+        <f>H29-J29*6</f>
+        <v/>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>toluene</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>poly(methyl methacrylate)</t>
         </is>
       </c>
-      <c r="P29" s="3" t="n">
+      <c r="R29" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in deuterium oxide (test5)</t>
-        </is>
-      </c>
-      <c r="S29" s="3">
-        <f>H29-J29*3</f>
-        <v/>
-      </c>
-      <c r="T29" s="3">
-        <f>H29-J29*6</f>
-        <v/>
       </c>
     </row>
     <row r="30">
@@ -6730,31 +6248,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="M30" s="3">
+        <f>H30-J30*3</f>
+        <v/>
+      </c>
+      <c r="N30" s="3">
+        <f>H30-J30*6</f>
+        <v/>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>toluene-d8</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>polystyrene</t>
         </is>
       </c>
-      <c r="P30" s="3" t="n">
+      <c r="R30" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in methanol-d4 (test5)</t>
-        </is>
-      </c>
-      <c r="S30" s="3">
-        <f>H30-J30*3</f>
-        <v/>
-      </c>
-      <c r="T30" s="3">
-        <f>H30-J30*6</f>
-        <v/>
       </c>
     </row>
     <row r="31">
@@ -6810,31 +6323,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="M31" s="3">
+        <f>H31-J31*3</f>
+        <v/>
+      </c>
+      <c r="N31" s="3">
+        <f>H31-J31*6</f>
+        <v/>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>water</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>poly(ethylene glycol) methyl ether acrylate</t>
         </is>
       </c>
-      <c r="P31" s="3" t="n">
+      <c r="R31" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in acetone-d6 (test5)</t>
-        </is>
-      </c>
-      <c r="S31" s="3">
-        <f>H31-J31*3</f>
-        <v/>
-      </c>
-      <c r="T31" s="3">
-        <f>H31-J31*6</f>
-        <v/>
       </c>
     </row>
     <row r="32">
@@ -6890,16 +6398,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in tetrahydrofuran-d8 (test5)</t>
-        </is>
-      </c>
-      <c r="S32" s="3">
+      <c r="M32" s="3">
         <f>H32-J32*3</f>
         <v/>
       </c>
-      <c r="T32" s="3">
+      <c r="N32" s="3">
         <f>H32-J32*6</f>
         <v/>
       </c>
@@ -6957,16 +6460,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in tetrahydrofuran-d8 (test5)</t>
-        </is>
-      </c>
-      <c r="S33" s="3">
+      <c r="M33" s="3">
         <f>H33-J33*3</f>
         <v/>
       </c>
-      <c r="T33" s="3">
+      <c r="N33" s="3">
         <f>H33-J33*6</f>
         <v/>
       </c>
@@ -7024,16 +6522,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in chloroform-d (test5)</t>
-        </is>
-      </c>
-      <c r="S34" s="3">
+      <c r="M34" s="3">
         <f>H34-J34*3</f>
         <v/>
       </c>
-      <c r="T34" s="3">
+      <c r="N34" s="3">
         <f>H34-J34*6</f>
         <v/>
       </c>
@@ -7091,16 +6584,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene oxide) in acetonitrile-d3 (test5)</t>
-        </is>
-      </c>
-      <c r="S35" s="3">
+      <c r="M35" s="3">
         <f>H35-J35*3</f>
         <v/>
       </c>
-      <c r="T35" s="3">
+      <c r="N35" s="3">
         <f>H35-J35*6</f>
         <v/>
       </c>
@@ -7158,16 +6646,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in toluene (test7)</t>
-        </is>
-      </c>
-      <c r="S36" s="3">
+      <c r="M36" s="3">
         <f>H36-J36*3</f>
         <v/>
       </c>
-      <c r="T36" s="3">
+      <c r="N36" s="3">
         <f>H36-J36*6</f>
         <v/>
       </c>
@@ -7225,16 +6708,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in benzene (test7)</t>
-        </is>
-      </c>
-      <c r="S37" s="3">
+      <c r="M37" s="3">
         <f>H37-J37*3</f>
         <v/>
       </c>
-      <c r="T37" s="3">
+      <c r="N37" s="3">
         <f>H37-J37*6</f>
         <v/>
       </c>
@@ -7292,16 +6770,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in acetone (test7)</t>
-        </is>
-      </c>
-      <c r="S38" s="3">
+      <c r="M38" s="3">
         <f>H38-J38*3</f>
         <v/>
       </c>
-      <c r="T38" s="3">
+      <c r="N38" s="3">
         <f>H38-J38*6</f>
         <v/>
       </c>
@@ -7359,16 +6832,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate) in tetrahydrofuran (test7)</t>
-        </is>
-      </c>
-      <c r="S39" s="3">
+      <c r="M39" s="3">
         <f>H39-J39*3</f>
         <v/>
       </c>
-      <c r="T39" s="3">
+      <c r="N39" s="3">
         <f>H39-J39*6</f>
         <v/>
       </c>
@@ -7426,6 +6894,8 @@
           <t>solvent</t>
         </is>
       </c>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7480,16 +6950,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>poly(butyl acrylate) in benzene (test7)</t>
-        </is>
-      </c>
-      <c r="S41" s="3">
+      <c r="M41" s="3">
         <f>H41-J41*3</f>
         <v/>
       </c>
-      <c r="T41" s="3">
+      <c r="N41" s="3">
         <f>H41-J41*6</f>
         <v/>
       </c>
@@ -7547,16 +7012,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>poly(butyl acrylate) in acetone (test7)</t>
-        </is>
-      </c>
-      <c r="S42" s="3">
+      <c r="M42" s="3">
         <f>H42-J42*3</f>
         <v/>
       </c>
-      <c r="T42" s="3">
+      <c r="N42" s="3">
         <f>H42-J42*6</f>
         <v/>
       </c>
@@ -7614,16 +7074,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>poly(butyl acrylate) in chloroform (test7)</t>
-        </is>
-      </c>
-      <c r="S43" s="3">
+      <c r="M43" s="3">
         <f>H43-J43*3</f>
         <v/>
       </c>
-      <c r="T43" s="3">
+      <c r="N43" s="3">
         <f>H43-J43*6</f>
         <v/>
       </c>
@@ -7681,6 +7136,8 @@
           <t>solvent</t>
         </is>
       </c>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -7735,16 +7192,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene glycol) methyl ether acrylate in water (test7)</t>
-        </is>
-      </c>
-      <c r="S45" s="3">
+      <c r="M45" s="3">
         <f>H45-J45*3</f>
         <v/>
       </c>
-      <c r="T45" s="3">
+      <c r="N45" s="3">
         <f>H45-J45*6</f>
         <v/>
       </c>
@@ -7802,16 +7254,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>poly(ethylene glycol) methyl ether acrylate in acetone (test7)</t>
-        </is>
-      </c>
-      <c r="S46" s="3">
+      <c r="M46" s="3">
         <f>H46-J46*3</f>
         <v/>
       </c>
-      <c r="T46" s="3">
+      <c r="N46" s="3">
         <f>H46-J46*6</f>
         <v/>
       </c>
@@ -7869,6 +7316,8 @@
           <t>solvent</t>
         </is>
       </c>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -7923,16 +7372,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>poly(methyl methacrylate-block-poly(ethylene glycol) methyl ether methacrylate) in acetone-d6 (test7)</t>
-        </is>
-      </c>
-      <c r="S48" s="3">
+      <c r="M48" s="3">
         <f>H48-J48*3</f>
         <v/>
       </c>
-      <c r="T48" s="3">
+      <c r="N48" s="3">
         <f>H48-J48*6</f>
         <v/>
       </c>
